--- a/Valores de tallas.xlsx
+++ b/Valores de tallas.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor_Occidente\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jestrada\Downloads\Monitor Occidente\Monitor_Occidente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26CE282-2C2A-4B99-9608-53144CE334F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20609443-3A05-467B-BDFE-1ECB099A61BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{579CB178-6F9F-43FC-A619-8BE3F16866CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Excepciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="58">
   <si>
     <t>ex1</t>
   </si>
@@ -189,6 +190,30 @@
   </si>
   <si>
     <t>Joven</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>CJ50914PNE</t>
+  </si>
+  <si>
+    <t>CJ50914PTA</t>
+  </si>
+  <si>
+    <t>CJ50919PNE</t>
+  </si>
+  <si>
+    <t>CJ401912P0NE</t>
+  </si>
+  <si>
+    <t>CJ401913P0NE</t>
+  </si>
+  <si>
+    <t>CJ414401P0NE</t>
+  </si>
+  <si>
+    <t>CJ414404P0NE</t>
   </si>
 </sst>
 </file>
@@ -1773,4 +1798,57 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9975E67-9394-4F4E-AB3F-4FCF32EE2576}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>